--- a/AAII_Financials/Quarterly/FIRRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FIRRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
   <si>
     <t>FIRRY</t>
   </si>
@@ -656,62 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,8 +750,17 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,8 +788,17 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -797,8 +826,17 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +848,11 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,8 +880,17 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,8 +918,17 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -897,8 +956,17 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -926,8 +994,17 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,8 +1013,11 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -965,8 +1045,17 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -994,8 +1083,17 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,8 +1105,11 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1036,8 +1137,17 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1065,8 +1175,17 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1094,8 +1213,17 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1123,8 +1251,17 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1152,8 +1289,17 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,8 +1327,17 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1210,8 +1365,17 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1239,8 +1403,17 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1441,17 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1479,17 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1517,17 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,8 +1555,17 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1384,8 +1593,17 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1413,8 +1631,17 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,8 +1669,17 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1471,42 +1707,60 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1772,11 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,269 +1788,353 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>229300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>265100</v>
+      </c>
+      <c r="F41" s="3">
+        <v>273300</v>
+      </c>
+      <c r="G41" s="3">
         <v>227100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>228100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>359100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>321300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>330400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>282200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>334200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>390600</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>304900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>137200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>591700</v>
+      </c>
+      <c r="G42" s="3">
         <v>726000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="H42" s="3">
         <v>712900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="I42" s="3">
         <v>141400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="J42" s="3">
         <v>354200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="K42" s="3">
         <v>325000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="L42" s="3">
         <v>258400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
         <v>154300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>152200</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>327400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>338800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>90500</v>
+      </c>
+      <c r="G43" s="3">
         <v>270300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>239400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>315400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>78700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>252000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>244400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>311000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>99600</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>182600</v>
+      </c>
+      <c r="F44" s="3">
+        <v>164100</v>
+      </c>
+      <c r="G44" s="3">
         <v>154300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>143900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>167700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>188300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>174800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>152400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>197600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>213500</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>359300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>57900</v>
+      </c>
+      <c r="G45" s="3">
         <v>165000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>38100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="I45" s="3">
         <v>216900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="J45" s="3">
         <v>73300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="K45" s="3">
         <v>42600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>38600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>79600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>56700</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1057200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1282900</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1179100</v>
+      </c>
+      <c r="G46" s="3">
         <v>1542800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>1364200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>1200500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>1017300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>1124800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>977800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>1076800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>914900</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>996600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>707100</v>
+      </c>
+      <c r="F47" s="3">
+        <v>507600</v>
+      </c>
+      <c r="G47" s="3">
         <v>288600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>320700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
         <v>549100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="J47" s="3">
         <v>541600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3">
         <v>667400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>608600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>593000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>564900</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>376300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>363400</v>
+      </c>
+      <c r="F48" s="3">
+        <v>354700</v>
+      </c>
+      <c r="G48" s="3">
         <v>335800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>337600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>337100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>335200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>337800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>328200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>335100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>342800</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>90900</v>
+      </c>
+      <c r="F49" s="3">
+        <v>90500</v>
+      </c>
+      <c r="G49" s="3">
         <v>90000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>90500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>92200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="J49" s="3">
         <v>92700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>96600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>94400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>95900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>98300</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +2162,17 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,13 +2200,22 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
@@ -1879,8 +2238,17 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2276,55 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2550200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2471800</v>
+      </c>
+      <c r="F54" s="3">
+        <v>2158500</v>
+      </c>
+      <c r="G54" s="3">
         <v>2282100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>2137800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>2204500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>2012800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>2252500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>2034100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>2126900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>1948600</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2336,11 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,182 +2352,239 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>382300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>796100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>627000</v>
+      </c>
+      <c r="G57" s="3">
         <v>769500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>639900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>748800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
         <v>633200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
         <v>814200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>673800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>749500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>624400</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G58" s="3">
         <v>31400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>32700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>30900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>40500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>11300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>2400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>575900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>257700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>166400</v>
+      </c>
+      <c r="G59" s="3">
         <v>223100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>135700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>209700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>143000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>203900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>91300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>195400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>134800</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1118200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1070600</v>
+      </c>
+      <c r="F60" s="3">
+        <v>869000</v>
+      </c>
+      <c r="G60" s="3">
         <v>1038300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>927600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>1002500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>890300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>1040900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>893800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>966200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>852400</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>68100</v>
+      </c>
+      <c r="F61" s="3">
+        <v>62100</v>
+      </c>
+      <c r="G61" s="3">
         <v>18200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>11900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>11300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>11900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>29600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>28700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>29100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G62" s="3">
         <v>2100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>4000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="K62" s="3">
         <v>3200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>3100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>5500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2612,17 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2650,17 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2688,55 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1254000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1196200</v>
+      </c>
+      <c r="F66" s="3">
+        <v>981700</v>
+      </c>
+      <c r="G66" s="3">
         <v>1098600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>982200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>1058300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>947100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>1116400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>965200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>1042800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2748,11 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2780,17 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2818,17 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2856,17 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2894,55 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>653600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>643900</v>
+      </c>
+      <c r="F72" s="3">
+        <v>554600</v>
+      </c>
+      <c r="G72" s="3">
         <v>570500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>546200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>552600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>476800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>521600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>476600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>487200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>411600</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2970,17 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +3008,17 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +3046,55 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1210200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1192200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1095300</v>
+      </c>
+      <c r="G76" s="3">
         <v>1101300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>1073900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>1073300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>994100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>1060700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>996100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>1010000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>943700</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,42 +3122,60 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2619,8 +3203,17 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,37 +3225,49 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
+        <v>37500</v>
+      </c>
+      <c r="G83" s="3">
         <v>-22000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>18800</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>39700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>-21600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>19500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +3295,17 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +3333,17 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +3371,17 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +3409,17 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3447,55 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>33400</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="G89" s="3">
         <v>97500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>43300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>12000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>-72400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>118300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>91900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>34200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-62700</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,37 +3507,49 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="G91" s="3">
         <v>-3900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-4400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="J91" s="3">
         <v>-3100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-5400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3577,17 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,37 +3615,55 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-162200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="F94" s="3">
+        <v>58500</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="H94" s="3">
         <v>-153200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="I94" s="3">
         <v>44900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>69400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>-92500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-91300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-71700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,37 +3675,49 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>300</v>
+      </c>
+      <c r="F96" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G96" s="3">
         <v>23700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="H96" s="3">
         <v>30800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="I96" s="3">
         <v>200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>200</v>
-      </c>
-      <c r="H96" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>48400</v>
       </c>
       <c r="J96" s="3">
         <v>200</v>
       </c>
       <c r="K96" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L96" s="3">
+        <v>48400</v>
+      </c>
+      <c r="M96" s="3">
+        <v>200</v>
+      </c>
+      <c r="N96" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3745,17 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3783,17 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,91 +3821,127 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>10600</v>
+      </c>
+      <c r="G100" s="3">
         <v>-17600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>-31900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>7900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-51400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-43400</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F102" s="3">
+        <v>43900</v>
+      </c>
+      <c r="G102" s="3">
         <v>-20900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>-141700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>55900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>23400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-50900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-37800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-90600</v>
       </c>
     </row>
